--- a/Table/Excel/Notebook.xlsx
+++ b/Table/Excel/Notebook.xlsx
@@ -522,12 +522,12 @@
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>마을 소개</t>
+          <t>@notebook.1.title</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>보라 마을. 겨울이 긴 언덕 마을. 꼭대기에 박물관이 있다.</t>
+          <t>@notebook.1.body</t>
         </is>
       </c>
     </row>
@@ -546,12 +546,12 @@
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>마을 지도</t>
+          <t>@notebook.2.title</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>광장, 중간 거주지, 꼭대기 지역, 녹지, 쓰레기장.</t>
+          <t>@notebook.2.body</t>
         </is>
       </c>
     </row>
@@ -570,12 +570,12 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>신분증</t>
+          <t>@notebook.3.title</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>직업: 사설탐정.</t>
+          <t>@notebook.3.body</t>
         </is>
       </c>
     </row>
@@ -598,12 +598,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>촌장님</t>
+          <t>@notebook.101.title</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>목도리 도마뱀. 보물 도난 사건을 비밀리에 맡겼다.</t>
+          <t>@notebook.101.body</t>
         </is>
       </c>
     </row>
@@ -626,12 +626,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>검맨</t>
+          <t>@notebook.102.title</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>껌으로 된 땅 주인. 친절하다. 주민들과 먼저 얼굴을 트라고 했다.</t>
+          <t>@notebook.102.body</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>지그</t>
+          <t>@notebook.103.title</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>바에서 청소 일을 한다. 광장 끝 허름한 집에 혼자 산다.</t>
+          <t>@notebook.103.body</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>어린쥐</t>
+          <t>@notebook.104.title</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>친구는 필요 없다지만 모든 정보를 안다고 한다. 사탕 가게 주인을 좋게 본다.</t>
+          <t>@notebook.104.body</t>
         </is>
       </c>
     </row>
@@ -710,12 +710,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>집배원</t>
+          <t>@notebook.105.title</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>마을의 모든 집 주소를 안다.</t>
+          <t>@notebook.105.body</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>거미의 알리바이</t>
+          <t>@notebook.201.title</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>바에서 하루종일 일한 뒤 바로 집으로 퇴근했다.</t>
+          <t>@notebook.201.body</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>코끼리의 알리바이</t>
+          <t>@notebook.202.title</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>낮에는 꽃집에 있다가 밤에 나와서 마을을 산책했다.</t>
+          <t>@notebook.202.body</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>보물은 무엇인가?</t>
+          <t>@notebook.301.title</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>촌장님의 전설에 따르면 하늘에서 떨어졌다고 한다.</t>
+          <t>@notebook.301.body</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>케이블카는 언제 고장 났나?</t>
+          <t>@notebook.302.title</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>보물이 사라진 밤, 케이블카도 멈췄다.</t>
+          <t>@notebook.302.body</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>바에 가 보기</t>
+          <t>@notebook.401.title</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>저녁이면 바가 붐빈다고 한다.</t>
+          <t>@notebook.401.body</t>
         </is>
       </c>
     </row>
